--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0001T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.433034373659253</v>
+        <v>1.207868085719629</v>
       </c>
       <c r="D2" t="n">
-        <v>7.462623867502817</v>
+        <v>1.212676378469208</v>
       </c>
       <c r="E2" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F2" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.9176193703658</v>
+        <v>4.211613147684442</v>
       </c>
       <c r="D3" t="n">
-        <v>27.89258755468204</v>
+        <v>4.532545477635832</v>
       </c>
       <c r="E3" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F3" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.80350850198276</v>
+        <v>3.705570131572198</v>
       </c>
       <c r="D4" t="n">
-        <v>21.53762680697854</v>
+        <v>3.499864356134013</v>
       </c>
       <c r="E4" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F4" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.8919664009433</v>
+        <v>4.207444540153287</v>
       </c>
       <c r="D5" t="n">
-        <v>24.7502871053777</v>
+        <v>4.021921654623877</v>
       </c>
       <c r="E5" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F5" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.98827910344663</v>
+        <v>5.198095354310077</v>
       </c>
       <c r="D6" t="n">
-        <v>24.19070247256913</v>
+        <v>3.930989151792484</v>
       </c>
       <c r="E6" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F6" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.51922858729391</v>
+        <v>2.196874645435261</v>
       </c>
       <c r="D7" t="n">
-        <v>8.514693182963201</v>
+        <v>1.38363764223152</v>
       </c>
       <c r="E7" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F7" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>41.17880123253637</v>
+        <v>6.691555200287159</v>
       </c>
       <c r="D8" t="n">
-        <v>33.60431519909311</v>
+        <v>5.460701219852631</v>
       </c>
       <c r="E8" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F8" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.78028474190124</v>
+        <v>6.626796270558952</v>
       </c>
       <c r="D9" t="n">
-        <v>34.23155404113856</v>
+        <v>5.562627531685016</v>
       </c>
       <c r="E9" t="n">
-        <v>11.15327391833672</v>
+        <v>1.812407011729717</v>
       </c>
       <c r="F9" t="n">
-        <v>9.486692314091707</v>
+        <v>1.541587501039903</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
